--- a/platform_core_data/supplier-features/ancillaries/shared/ancillaries-baseline/test_design/TestCases_AncillariesSeatMap.xlsx
+++ b/platform_core_data/supplier-features/ancillaries/shared/ancillaries-baseline/test_design/TestCases_AncillariesSeatMap.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$P$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$T$125</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -678,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -698,6 +698,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1">
@@ -794,6 +795,11 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Review</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Setup Group</t>
         </is>
       </c>
     </row>
@@ -868,6 +874,11 @@
       <c r="S2" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -940,6 +951,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1010,6 +1026,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1081,6 +1102,11 @@
       <c r="S5" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -1153,6 +1179,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1223,6 +1254,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1301,6 +1337,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1371,6 +1412,11 @@
       <c r="S9" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -1443,6 +1489,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1511,6 +1562,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1582,6 +1638,11 @@
       <c r="S12" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>11 Second flight on a different aircraft</t>
         </is>
       </c>
     </row>
@@ -1654,6 +1715,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1724,6 +1790,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1796,6 +1867,11 @@
       <c r="S15" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -1868,6 +1944,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1938,6 +2019,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -2018,6 +2104,11 @@
       <c r="S18" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -2091,6 +2182,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -2161,6 +2257,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -2230,6 +2331,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -2308,6 +2414,11 @@
       <c r="S22" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -2379,6 +2490,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -2447,6 +2563,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -2519,6 +2640,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -2587,6 +2713,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -2662,6 +2793,11 @@
       <c r="S27" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -2734,6 +2870,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="2" t="n">
@@ -2809,6 +2950,11 @@
       <c r="S29" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -2881,6 +3027,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2950,6 +3101,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -3020,6 +3176,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -3112,6 +3273,11 @@
       <c r="S33" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -3189,6 +3355,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -3263,6 +3434,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -3338,6 +3514,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -3429,6 +3610,11 @@
       <c r="S37" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -3499,6 +3685,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -3572,6 +3763,11 @@
       <c r="S39" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -3644,6 +3840,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -3718,6 +3919,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>03 2 adults (Mr + Ms) - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -3797,6 +4003,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>03 2 adults (Mr + Ms) - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -3878,6 +4089,11 @@
       <c r="S43" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>03 2 adults (Mr + Ms) - one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -3949,6 +4165,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -4027,6 +4248,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>03 2 adults (Mr + Ms) - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -4104,6 +4330,11 @@
       <c r="S46" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -4175,6 +4406,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -4245,6 +4481,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -4321,6 +4562,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>13 Ends the booking - a fresh default booking each, run last</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -4391,6 +4637,11 @@
       <c r="S50" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -4462,6 +4713,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="25" t="n">
@@ -4551,6 +4807,11 @@
       <c r="S52" s="27" t="inlineStr">
         <is>
           <t>Rejected</t>
+        </is>
+      </c>
+      <c r="T52" s="27" t="inlineStr">
+        <is>
+          <t>19 Two sessions at once</t>
         </is>
       </c>
     </row>
@@ -4625,6 +4886,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>13 Ends the booking - a fresh default booking each, run last</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -4697,6 +4963,11 @@
       <c r="S54" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -4768,6 +5039,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -4847,6 +5123,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -4927,6 +5208,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -5006,6 +5292,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="2" t="n">
@@ -5083,6 +5374,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -5163,6 +5459,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -5241,6 +5542,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>18 Live connection only</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -5315,6 +5621,11 @@
       <c r="S62" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -5386,6 +5697,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="150" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -5455,6 +5771,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="150" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -5526,6 +5847,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -5599,6 +5925,11 @@
       <c r="S66" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -5677,6 +6008,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="150" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -5752,6 +6088,11 @@
       <c r="S68" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -5827,6 +6168,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="150" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -5900,6 +6246,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="150" customHeight="1">
       <c r="A71" s="2" t="n">
@@ -5973,6 +6324,11 @@
       <c r="S71" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -6046,6 +6402,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>13 Ends the booking - a fresh default booking each, run last</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="150" customHeight="1">
       <c r="A73" s="2" t="n">
@@ -6115,6 +6476,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="150" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -6183,6 +6549,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="150" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -6253,6 +6624,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>04 1 adult alone - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="150" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -6323,6 +6699,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>06 1 adult + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="150" customHeight="1">
       <c r="A77" s="2" t="n">
@@ -6396,6 +6777,11 @@
       <c r="S77" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>05 1 adult + 1 child - one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -6467,6 +6853,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>05 1 adult + 1 child - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="150" customHeight="1">
       <c r="A79" s="2" t="n">
@@ -6538,6 +6929,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>07 2 adults + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="150" customHeight="1">
       <c r="A80" s="25" t="n">
@@ -6627,6 +7023,11 @@
       <c r="S80" s="27" t="inlineStr">
         <is>
           <t>Rejected</t>
+        </is>
+      </c>
+      <c r="T80" s="27" t="inlineStr">
+        <is>
+          <t>06 1 adult + 1 infant - one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -6705,6 +7106,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="120" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -6781,6 +7187,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="120" customHeight="1">
       <c r="A83" s="2" t="n">
@@ -6857,6 +7268,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T83" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="120" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -6933,6 +7349,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>10 Multi-city, 3 journeys, one connecting - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="120" customHeight="1">
       <c r="A85" s="2" t="n">
@@ -7009,6 +7430,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T85" s="4" t="inlineStr">
+        <is>
+          <t>15 Booked - multi-city (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="120" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -7085,6 +7511,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T86" s="4" t="inlineStr">
+        <is>
+          <t>10 Multi-city, 3 journeys, one connecting - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="120" customHeight="1">
       <c r="A87" s="2" t="n">
@@ -7161,6 +7592,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T87" s="4" t="inlineStr">
+        <is>
+          <t>15 Booked - multi-city (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="120" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -7237,6 +7673,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T88" s="4" t="inlineStr">
+        <is>
+          <t>10 Multi-city, 3 journeys, one connecting - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="120" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -7313,6 +7754,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T89" s="4" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="120" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -7390,6 +7836,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="120" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -7465,6 +7916,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T91" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="120" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -7540,6 +7996,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T92" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="120" customHeight="1">
       <c r="A93" s="2" t="n">
@@ -7615,6 +8076,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T93" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="120" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -7706,6 +8172,11 @@
       <c r="S94" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
         </is>
       </c>
     </row>
@@ -7784,6 +8255,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T95" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="120" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -7877,6 +8353,11 @@
       <c r="S96" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T96" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
         </is>
       </c>
     </row>
@@ -7955,6 +8436,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T97" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="120" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -8046,6 +8532,11 @@
       <c r="S98" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
         </is>
       </c>
     </row>
@@ -8125,6 +8616,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T99" s="4" t="inlineStr">
+        <is>
+          <t>13 Ends the booking - a fresh default booking each, run last</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="120" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -8219,6 +8715,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T100" s="4" t="inlineStr">
+        <is>
+          <t>16 Booking fails on purpose - baggage clash (presses Book)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="120" customHeight="1">
       <c r="A101" s="2" t="n">
@@ -8312,6 +8813,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T101" s="4" t="inlineStr">
+        <is>
+          <t>16 Booking fails on purpose - baggage clash (presses Book)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="120" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -8404,6 +8910,11 @@
       <c r="S102" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T102" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
         </is>
       </c>
     </row>
@@ -8501,6 +9012,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T103" s="4" t="inlineStr">
+        <is>
+          <t>08 2 adults + 2 infants - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="150" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -8592,6 +9108,11 @@
       <c r="S104" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="T104" s="4" t="inlineStr">
+        <is>
+          <t>12 Supplier credential not in EGP</t>
         </is>
       </c>
     </row>
@@ -8666,6 +9187,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T105" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="150" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -8738,6 +9264,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T106" s="4" t="inlineStr">
+        <is>
+          <t>05 1 adult + 1 child - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="150" customHeight="1">
       <c r="A107" s="2" t="n">
@@ -8810,6 +9341,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T107" s="4" t="inlineStr">
+        <is>
+          <t>06 1 adult + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="150" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -8885,6 +9421,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T108" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="150" customHeight="1">
       <c r="A109" s="2" t="n">
@@ -8959,6 +9500,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T109" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="150" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -9032,6 +9578,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T110" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="150" customHeight="1">
       <c r="A111" s="2" t="n">
@@ -9103,6 +9654,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T111" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="150" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -9175,6 +9731,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T112" s="4" t="inlineStr">
+        <is>
+          <t>05 1 adult + 1 child - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="150" customHeight="1">
       <c r="A113" s="2" t="n">
@@ -9247,6 +9808,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T113" s="4" t="inlineStr">
+        <is>
+          <t>06 1 adult + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="150" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -9320,6 +9886,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T114" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="150" customHeight="1">
       <c r="A115" s="2" t="n">
@@ -9393,6 +9964,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T115" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="150" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -9464,6 +10040,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T116" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="150" customHeight="1">
       <c r="A117" s="2" t="n">
@@ -9537,6 +10118,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T117" s="4" t="inlineStr">
+        <is>
+          <t>17 Held, then paid (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="150" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -9610,6 +10196,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T118" s="4" t="inlineStr">
+        <is>
+          <t>17 Held, then paid (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="150" customHeight="1">
       <c r="A119" s="2" t="n">
@@ -9682,6 +10273,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T119" s="4" t="inlineStr">
+        <is>
+          <t>17 Held, then paid (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="150" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -9753,6 +10349,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T120" s="33" t="inlineStr">
+        <is>
+          <t>17 Held, then paid (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="150" customHeight="1">
       <c r="A121" s="2" t="n">
@@ -9826,6 +10427,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T121" s="4" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="150" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -9899,6 +10505,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T122" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="150" customHeight="1">
       <c r="A123" s="2" t="n">
@@ -9973,6 +10584,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T123" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="150" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -10046,6 +10662,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T124" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="150" customHeight="1">
       <c r="A125" s="2" t="n">
@@ -10120,6 +10741,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="T125" s="4" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="150" customHeight="1"/>
     <row r="127" ht="150" customHeight="1"/>
@@ -10127,7 +10753,7 @@
     <row r="129" ht="150" customHeight="1"/>
     <row r="130" ht="150" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:P80"/>
+  <autoFilter ref="A1:T125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -10139,7 +10765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10372,6 +10998,253 @@
       <c r="A25" s="13" t="inlineStr">
         <is>
           <t>The system refuses a second booking for a passenger whose name, date of birth and document already have one. It returns a clear message that is NEVER shown on screen, so the booking simply appears to do nothing. This is not a seat-map test - it is a constraint on how the tests are run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20.1" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Setup groups - one booking per group</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>The 'Setup Group' column on the Test Cases sheet says which booking each test runs on. Build that booking once and run every test in the group on it before building the next one. Run the groups in number order. Within a group, change the fare package on step 1 instead of building a new booking. Start a fresh booking only when a test changes or ends the one you are on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>01 Default - 1 adult + 1 child + 1 infant, one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Search CAI-JED with 1 adult + 1 child + 1 infant, Economy. Most tests run here. Start with the step 1 tests (NAV-001, NAV-002, NAV-002b, GEN-003) and the price-change tests (FRC-001, FRC-003, then FRC-002 and FRC-005) - the infant in the search is what brings up the 'Price Update' pop-up. Then choose 'Plus' and run the Plus tests, and switch to 'Value' on step 1 for the Value tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>02 Business - same flight as group 01</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>The SAME flight as group 01, searched again in Business with the 'Premium' package. CAB-001 and CAB-005 compare it with what group 01 recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>03 2 adults (Mr + Ms) - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>2 adults, one with the title 'Mr' and one 'Ms'. For the women-only seat tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>04 1 adult alone - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>1 adult on their own - no child, no infant. The exit-seat starting point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>05 1 adult + 1 child - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>1 adult + 1 child and NO infant: with an infant the adult could not take an exit seat at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>06 1 adult + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>1 adult + 1 infant, with the infant linked to that adult on step 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>07 2 adults + 1 infant - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>2 adults + 1 infant, with the infant linked to adult A first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>08 2 adults + 2 infants - one-way, Economy</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>2 adults + 2 infants, each infant linked to a different adult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>09 Return trip - default passengers, Economy</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>A return trip with the default passengers. One seat map per journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>10 Multi-city, 3 journeys, one connecting - default passengers, Economy</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>CAI-JED, JED-RUH (connecting through DMM), RUH-CAI, with the default passengers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>11 Second flight on a different aircraft</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>A second flight that uses a different aircraft type from group 01's flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>12 Supplier credential not in EGP</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>An offer from a supplier credential whose currency is not EGP. Note its rate of exchange first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>13 Ends the booking - a fresh default booking each, run last</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Each of these ends the booking (time limit, expired session, page left, broken link). Run them after the other groups, each on a fresh default booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>14 Booked - default, with seat, meal and bag (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>ONE real booking with the default passengers, a seat, a meal and an extra bag. Every confirmation, e-ticket, wallet and report test reads this same booking. Needs booking approval for the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>15 Booked - multi-city (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>The group 10 trip, finished with 'Book'. Needs booking approval for the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>16 Booking fails on purpose - baggage clash (presses Book)</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>A package that already includes checked baggage, plus an extra bag of the SAME weight, then 'Book'. The booking is expected to fail. Needs booking approval for the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>17 Held, then paid (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Hold a booking with a seat, a meal and a bag, then pay it. Needs booking approval for the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>18 Live connection only</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Cannot run on staging. Waits for the live connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>19 Two sessions at once</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Two browser sessions on the same flight. This test is Rejected and is not run.</t>
         </is>
       </c>
     </row>
@@ -10688,7 +11561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10709,8 +11582,9 @@
           <t>Tests in this sheet</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>79</v>
+      <c r="B3">
+        <f>COUNTA('Test Cases'!$B$2:$B$2000)</f>
+        <v/>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -10731,11 +11605,12 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>15</v>
+      <c r="B6">
+        <f>COUNTIF('Test Cases'!$F$2:$F$2000,$A6)</f>
+        <v/>
       </c>
       <c r="C6">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$80,$A6,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$2000,$A6,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10745,11 +11620,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>41</v>
+      <c r="B7">
+        <f>COUNTIF('Test Cases'!$F$2:$F$2000,$A7)</f>
+        <v/>
       </c>
       <c r="C7">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$80,$A7,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$2000,$A7,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10759,11 +11635,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>20</v>
+      <c r="B8">
+        <f>COUNTIF('Test Cases'!$F$2:$F$2000,$A8)</f>
+        <v/>
       </c>
       <c r="C8">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$80,$A8,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$2000,$A8,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10773,11 +11650,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3</v>
+      <c r="B9">
+        <f>COUNTIF('Test Cases'!$F$2:$F$2000,$A9)</f>
+        <v/>
       </c>
       <c r="C9">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$80,$A9,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$2000,$A9,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10794,8 +11672,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>67</v>
+      <c r="B12">
+        <f>COUNTIF('Test Cases'!$J$2:$J$2000,$A12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -10804,8 +11683,9 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>10</v>
+      <c r="B13">
+        <f>COUNTIF('Test Cases'!$J$2:$J$2000,$A13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -10814,8 +11694,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2</v>
+      <c r="B14">
+        <f>COUNTIF('Test Cases'!$J$2:$J$2000,$A14)</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -10831,11 +11712,12 @@
           <t>A. Getting to the seat map</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
+      <c r="B17">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A17)</f>
+        <v/>
       </c>
       <c r="C17">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A17,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A17,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10845,11 +11727,12 @@
           <t>B. How the map is drawn</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>7</v>
+      <c r="B18">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A18)</f>
+        <v/>
       </c>
       <c r="C18">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A18,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A18,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10859,11 +11742,12 @@
           <t>C. Seat colours and labels</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>5</v>
+      <c r="B19">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A19)</f>
+        <v/>
       </c>
       <c r="C19">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A19,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A19,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10873,11 +11757,12 @@
           <t>D. Choosing a seat</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>9</v>
+      <c r="B20">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A20)</f>
+        <v/>
       </c>
       <c r="C20">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A20,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A20,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10887,11 +11772,12 @@
           <t>E. More than one passenger or flight</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>4</v>
+      <c r="B21">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A21)</f>
+        <v/>
       </c>
       <c r="C21">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A21,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A21,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10901,11 +11787,12 @@
           <t>F. Prices</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>5</v>
+      <c r="B22">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A22)</f>
+        <v/>
       </c>
       <c r="C22">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A22,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A22,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10915,11 +11802,12 @@
           <t>G. Fare packages</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>4</v>
+      <c r="B23">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A23)</f>
+        <v/>
       </c>
       <c r="C23">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A23,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A23,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10929,11 +11817,12 @@
           <t>H. Women-only seats</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>6</v>
+      <c r="B24">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A24)</f>
+        <v/>
       </c>
       <c r="C24">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A24,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A24,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10943,11 +11832,12 @@
           <t>I. Keeping the choice</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>4</v>
+      <c r="B25">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A25)</f>
+        <v/>
       </c>
       <c r="C25">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A25,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A25,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10957,11 +11847,12 @@
           <t>J. Errors and clashes</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>3</v>
+      <c r="B26">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A26)</f>
+        <v/>
       </c>
       <c r="C26">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A26,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A26,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10971,11 +11862,12 @@
           <t>K. Small screens and screen readers</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>2</v>
+      <c r="B27">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A27)</f>
+        <v/>
       </c>
       <c r="C27">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A27,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A27,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10985,11 +11877,12 @@
           <t>L. Economy and Business</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>6</v>
+      <c r="B28">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A28)</f>
+        <v/>
       </c>
       <c r="C28">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A28,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A28,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -10999,11 +11892,12 @@
           <t>M. Adults, children and infants</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>5</v>
+      <c r="B29">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A29)</f>
+        <v/>
       </c>
       <c r="C29">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A29,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A29,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -11013,11 +11907,12 @@
           <t>N. Price change before booking</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>4</v>
+      <c r="B30">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A30)</f>
+        <v/>
       </c>
       <c r="C30">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A30,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A30,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -11027,11 +11922,12 @@
           <t>O. System problems</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>4</v>
+      <c r="B31">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A31)</f>
+        <v/>
       </c>
       <c r="C31">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A31,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A31,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -11041,33 +11937,139 @@
           <t>P. Emergency exit seats</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>6</v>
+      <c r="B32">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A32)</f>
+        <v/>
       </c>
       <c r="C32">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$80,$A32,'Test Cases'!$N$2:$N$80,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A32,'Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q. Completing the booking (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A33)</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A33,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S. Seat map on return and multi-city trips</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A34)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A34,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T. Meals</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A35)</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A35,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U. Extra baggage</t>
+        </is>
+      </c>
+      <c r="B36">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A36)</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A36,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V. Holding a booking (CREATES A REAL HELD BOOKING)</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A37)</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A37,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>W. Paying for a held booking (SPENDS REAL MONEY)</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A38)</f>
+        <v/>
+      </c>
+      <c r="C38">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A38,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>X. Reports</t>
+        </is>
+      </c>
+      <c r="B39">
+        <f>COUNTIF('Test Cases'!$C$2:$C$2000,$A39)</f>
+        <v/>
+      </c>
+      <c r="C39">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$2000,$A39,'Test Cases'!$N$2:$N$2000,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>Passed so far</t>
         </is>
       </c>
-      <c r="B34">
-        <f>COUNTIF('Test Cases'!$N$2:$N$80,"Pass")</f>
+      <c r="B41">
+        <f>COUNTIF('Test Cases'!$N$2:$N$2000,"Pass")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Failed so far</t>
         </is>
       </c>
-      <c r="B35">
-        <f>COUNTIF('Test Cases'!$N$2:$N$80,"Fail")</f>
+      <c r="B42">
+        <f>COUNTIF('Test Cases'!$N$2:$N$2000,"Fail")</f>
         <v/>
       </c>
     </row>
